--- a/Matlab/Active/TolStack.xlsx
+++ b/Matlab/Active/TolStack.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kla-my.sharepoint.com/personal/tyler_seawright_kla_com/Documents/Documents/ASPE ERROR BUDGET 2025/Matlab/Active/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tyman\OneDrive\Documents\GitHub\TolStack\Matlab\Active\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2973" documentId="14_{124E1256-161A-47F0-9292-96BB218273F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5BC4948-D477-42A9-914A-FCB4076638EB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA142C51-15AF-4D09-8978-FF217D089E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TolStack" sheetId="3" r:id="rId1"/>
@@ -34,8 +34,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -821,7 +819,7 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -832,12 +830,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1012,10 +1010,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1439,16 +1433,16 @@
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="76" t="s">
+      <c r="C10" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="76"/>
-      <c r="E10" s="76"/>
-      <c r="F10" s="76" t="s">
+      <c r="D10" s="78"/>
+      <c r="E10" s="78"/>
+      <c r="F10" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="76"/>
-      <c r="H10" s="76"/>
+      <c r="G10" s="78"/>
+      <c r="H10" s="78"/>
       <c r="I10" s="6"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1671,16 +1665,16 @@
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="76" t="s">
+      <c r="C20" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="76"/>
-      <c r="E20" s="76"/>
-      <c r="F20" s="76" t="s">
+      <c r="D20" s="78"/>
+      <c r="E20" s="78"/>
+      <c r="F20" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="76"/>
-      <c r="H20" s="76"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="78"/>
       <c r="I20" s="6"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1793,10 +1787,10 @@
       <c r="C25" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D25" s="77" t="s">
+      <c r="D25" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="E25" s="77"/>
+      <c r="E25" s="76"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="36" t="s">
@@ -1808,10 +1802,10 @@
       <c r="C26" s="37">
         <v>1000</v>
       </c>
-      <c r="D26" s="72" t="s">
+      <c r="D26" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="E26" s="72"/>
+      <c r="E26" s="77"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="36" t="s">
@@ -1823,10 +1817,10 @@
       <c r="C27" s="37">
         <v>3</v>
       </c>
-      <c r="D27" s="72" t="s">
+      <c r="D27" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="72"/>
+      <c r="E27" s="77"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
@@ -1978,16 +1972,16 @@
         <v>53</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="76" t="s">
+      <c r="C6" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76" t="s">
+      <c r="D6" s="78"/>
+      <c r="E6" s="78"/>
+      <c r="F6" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
+      <c r="G6" s="78"/>
+      <c r="H6" s="78"/>
       <c r="I6" s="6"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -2221,16 +2215,16 @@
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
-      <c r="C16" s="76" t="s">
+      <c r="C16" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="76"/>
-      <c r="E16" s="76"/>
-      <c r="F16" s="76" t="s">
+      <c r="D16" s="78"/>
+      <c r="E16" s="78"/>
+      <c r="F16" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="76"/>
-      <c r="H16" s="76"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="78"/>
       <c r="I16" s="6"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -3405,10 +3399,10 @@
       <c r="C63" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D63" s="77" t="s">
+      <c r="D63" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="E63" s="77"/>
+      <c r="E63" s="76"/>
       <c r="F63" s="61"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -3421,10 +3415,10 @@
       <c r="C64" s="47">
         <v>1000</v>
       </c>
-      <c r="D64" s="78" t="s">
+      <c r="D64" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="E64" s="78"/>
+      <c r="E64" s="72"/>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="46" t="s">
@@ -3436,10 +3430,10 @@
       <c r="C65" s="47">
         <v>3</v>
       </c>
-      <c r="D65" s="78" t="s">
+      <c r="D65" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="E65" s="78"/>
+      <c r="E65" s="72"/>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
@@ -3696,6 +3690,10 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="D64:E64"/>
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="C16:E16"/>
@@ -3709,10 +3707,6 @@
     <mergeCell ref="F40:H40"/>
     <mergeCell ref="C56:E56"/>
     <mergeCell ref="F56:H56"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="F67:H67"/>
-    <mergeCell ref="D64:E64"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4362,10 +4356,10 @@
       <c r="C29" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D29" s="77" t="s">
+      <c r="D29" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="E29" s="77"/>
+      <c r="E29" s="76"/>
       <c r="F29" s="61"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -4378,10 +4372,10 @@
       <c r="C30" s="64">
         <v>1000</v>
       </c>
-      <c r="D30" s="78" t="s">
+      <c r="D30" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="E30" s="78"/>
+      <c r="E30" s="72"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="46" t="s">
@@ -4393,10 +4387,10 @@
       <c r="C31" s="47">
         <v>3</v>
       </c>
-      <c r="D31" s="78" t="s">
+      <c r="D31" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="E31" s="78"/>
+      <c r="E31" s="72"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="46" t="s">
@@ -6174,10 +6168,10 @@
       <c r="C26" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D26" s="77" t="s">
+      <c r="D26" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="E26" s="77"/>
+      <c r="E26" s="76"/>
       <c r="F26" s="61"/>
       <c r="K26" s="7" t="s">
         <v>7</v>
@@ -6188,10 +6182,10 @@
       <c r="M26" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="N26" s="77" t="s">
+      <c r="N26" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="O26" s="77"/>
+      <c r="O26" s="76"/>
       <c r="P26" s="61"/>
       <c r="U26" s="7" t="s">
         <v>7</v>
@@ -6202,10 +6196,10 @@
       <c r="W26" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="X26" s="77" t="s">
+      <c r="X26" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="Y26" s="77"/>
+      <c r="Y26" s="76"/>
       <c r="Z26" s="61"/>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.25">
@@ -6218,10 +6212,10 @@
       <c r="C27" s="64">
         <v>1000</v>
       </c>
-      <c r="D27" s="78" t="s">
+      <c r="D27" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="E27" s="78"/>
+      <c r="E27" s="72"/>
       <c r="K27" s="46" t="s">
         <v>37</v>
       </c>
@@ -6231,10 +6225,10 @@
       <c r="M27" s="64">
         <v>1000</v>
       </c>
-      <c r="N27" s="78" t="s">
+      <c r="N27" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="O27" s="78"/>
+      <c r="O27" s="72"/>
       <c r="U27" s="46" t="s">
         <v>37</v>
       </c>
@@ -6244,10 +6238,10 @@
       <c r="W27" s="64">
         <v>1000</v>
       </c>
-      <c r="X27" s="78" t="s">
+      <c r="X27" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="Y27" s="78"/>
+      <c r="Y27" s="72"/>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" s="46" t="s">
@@ -6259,10 +6253,10 @@
       <c r="C28" s="47">
         <v>3</v>
       </c>
-      <c r="D28" s="78" t="s">
+      <c r="D28" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="78"/>
+      <c r="E28" s="72"/>
       <c r="K28" s="46" t="s">
         <v>42</v>
       </c>
@@ -6272,10 +6266,10 @@
       <c r="M28" s="47">
         <v>3</v>
       </c>
-      <c r="N28" s="78" t="s">
+      <c r="N28" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="O28" s="78"/>
+      <c r="O28" s="72"/>
       <c r="U28" s="46" t="s">
         <v>42</v>
       </c>
@@ -6285,10 +6279,10 @@
       <c r="W28" s="47">
         <v>3</v>
       </c>
-      <c r="X28" s="78" t="s">
+      <c r="X28" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="Y28" s="78"/>
+      <c r="Y28" s="72"/>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" s="46" t="s">
@@ -6915,6 +6909,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="F65:H65"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="X27:Y27"/>
+    <mergeCell ref="X28:Y28"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="D26:E26"/>
     <mergeCell ref="M31:O31"/>
     <mergeCell ref="P31:R31"/>
     <mergeCell ref="W5:Y5"/>
@@ -6931,19 +6938,6 @@
     <mergeCell ref="N28:O28"/>
     <mergeCell ref="M5:O5"/>
     <mergeCell ref="X26:Y26"/>
-    <mergeCell ref="X27:Y27"/>
-    <mergeCell ref="X28:Y28"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="F65:H65"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7520,10 +7514,10 @@
       <c r="C27" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D27" s="77" t="s">
+      <c r="D27" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="E27" s="77"/>
+      <c r="E27" s="76"/>
       <c r="F27" s="61"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -7536,10 +7530,10 @@
       <c r="C28" s="64">
         <v>1000</v>
       </c>
-      <c r="D28" s="78" t="s">
+      <c r="D28" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="E28" s="78"/>
+      <c r="E28" s="72"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="46" t="s">
@@ -7551,10 +7545,10 @@
       <c r="C29" s="47">
         <v>3</v>
       </c>
-      <c r="D29" s="78" t="s">
+      <c r="D29" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="E29" s="78"/>
+      <c r="E29" s="72"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="46" t="s">
@@ -8215,10 +8209,10 @@
       <c r="C23" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D23" s="77" t="s">
+      <c r="D23" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="E23" s="77"/>
+      <c r="E23" s="76"/>
       <c r="F23" s="61"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -8231,10 +8225,10 @@
       <c r="C24" s="64">
         <v>1000</v>
       </c>
-      <c r="D24" s="78" t="s">
+      <c r="D24" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="E24" s="78"/>
+      <c r="E24" s="72"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="46" t="s">
@@ -8246,10 +8240,10 @@
       <c r="C25" s="47">
         <v>3</v>
       </c>
-      <c r="D25" s="78" t="s">
+      <c r="D25" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="78"/>
+      <c r="E25" s="72"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="46" t="s">
@@ -9373,10 +9367,10 @@
       <c r="C39" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D39" s="77" t="s">
+      <c r="D39" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="E39" s="77"/>
+      <c r="E39" s="76"/>
       <c r="F39" s="61"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -9389,10 +9383,10 @@
       <c r="C40" s="64">
         <v>1000</v>
       </c>
-      <c r="D40" s="78" t="s">
+      <c r="D40" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="E40" s="78"/>
+      <c r="E40" s="72"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="46" t="s">
@@ -9404,10 +9398,10 @@
       <c r="C41" s="47">
         <v>3</v>
       </c>
-      <c r="D41" s="78" t="s">
+      <c r="D41" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="E41" s="78"/>
+      <c r="E41" s="72"/>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="46" t="s">
@@ -10324,10 +10318,10 @@
       <c r="C31" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D31" s="77" t="s">
+      <c r="D31" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="E31" s="77"/>
+      <c r="E31" s="76"/>
       <c r="F31" s="61"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -10340,10 +10334,10 @@
       <c r="C32" s="64">
         <v>1000</v>
       </c>
-      <c r="D32" s="78" t="s">
+      <c r="D32" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="E32" s="78"/>
+      <c r="E32" s="72"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="46" t="s">
@@ -10355,10 +10349,10 @@
       <c r="C33" s="47">
         <v>3</v>
       </c>
-      <c r="D33" s="78" t="s">
+      <c r="D33" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="E33" s="78"/>
+      <c r="E33" s="72"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="46" t="s">
@@ -10557,9 +10551,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10786,27 +10783,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{212CAE50-2F1F-4036-9BDE-3178FFC470C0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{332012B1-D69D-4B4B-BD86-04053F3E929A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="c0d17589-4d0e-4e5b-b325-ec8c16a86cc3"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7d5420f2-a1e8-4afa-a52e-75a8a8141b9a"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10831,9 +10816,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{332012B1-D69D-4B4B-BD86-04053F3E929A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{212CAE50-2F1F-4036-9BDE-3178FFC470C0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="c0d17589-4d0e-4e5b-b325-ec8c16a86cc3"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7d5420f2-a1e8-4afa-a52e-75a8a8141b9a"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>